--- a/event_planner_forms/016_santa_claus_parade_volunteer_registration_form--event_planner_forms.xlsx
+++ b/event_planner_forms/016_santa_claus_parade_volunteer_registration_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Favorite Time Of Day</t>
+          <t>Favorite Time Of Day1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Favorite Holiday</t>
+          <t>Favorite Holiday1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Favorite Time Of Day</t>
+          <t>Favorite Time Of Day2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Favorite Day Of Week</t>
+          <t>Favorite Day Of Week9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'buddy_the_elf'}</t>
+          <t>buddy_the_elf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Buddy The Elf'}</t>
+          <t>Buddy The Elf</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'the_big_guy'}</t>
+          <t>the_big_guy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'The Big Guy'}</t>
+          <t>The Big Guy</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'candy_cane'}</t>
+          <t>candy_cane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Candy Cane'}</t>
+          <t>Candy Cane</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'cookie'}</t>
+          <t>cookie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Cookie'}</t>
+          <t>Cookie</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'cake'}</t>
+          <t>cake</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Cake'}</t>
+          <t>Cake</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
